--- a/AAII_Financials/Quarterly/OKE_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/OKE_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="92">
   <si>
     <t>OKE</t>
   </si>
@@ -656,543 +656,556 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AP102"/>
+  <dimension ref="A5:AQ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="42" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="43" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43830</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43738</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43646</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43555</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43465</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43373</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43190</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43100</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>43008</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42916</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42825</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42735</v>
       </c>
-      <c r="AP7" s="2">
+      <c r="AQ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>12049000</v>
+      </c>
+      <c r="E8" s="3">
         <v>9618000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>9065000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>8634000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>7887000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>8043000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>7000000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>5023000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>4894000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>4781000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>5235000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>4189000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>3732000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>4521000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>5032000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>5913500</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>5996700</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>5444600</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>5420500</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>4536200</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>3389000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>3194700</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>2570600</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>2174300</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>1660700</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>2136700</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>2663600</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>2263200</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>2457600</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>2780000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>3136700</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>3393900</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>2960500</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>3102100</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>3792200</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>2906400</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>2725800</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>2749600</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>2654500</v>
       </c>
-      <c r="AP8" s="3">
+      <c r="AQ8" s="3">
         <v>2357900</v>
       </c>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>9242000</v>
+      </c>
+      <c r="E9" s="3">
         <v>7053000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>6396000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>5962000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>5360000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>5655000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>4496000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>3027000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>2891000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>2897000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>3301000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>2799000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>2482000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>3347000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>4168000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>5011100</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>5108700</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>4580400</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>4574600</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>3674500</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>2579300</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>2328700</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>1849500</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>1439200</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>1130600</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>1452000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>2021300</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>1631100</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>1830600</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>2161900</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>2531800</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>2767000</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>2377900</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>2549200</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>3265500</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>2409100</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>2281800</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>2305900</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AP9" s="3">
         <v>2201300</v>
       </c>
-      <c r="AP9" s="3">
+      <c r="AQ9" s="3">
         <v>1917300</v>
       </c>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>2807000</v>
+      </c>
+      <c r="E10" s="3">
         <v>2565000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>2669000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>2672000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>2527000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>2388000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>2504000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1996000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>2003000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1884000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1934000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1390000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1250000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1174000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>864000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>902400</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>888000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>864200</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>845900</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>861700</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>809700</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>866000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>721100</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>735100</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>530100</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>684700</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>642300</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>632100</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>627000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>618100</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>604900</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>626900</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>582600</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>552900</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>526700</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>497300</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>444000</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>443700</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AP10" s="3">
         <v>453200</v>
       </c>
-      <c r="AP10" s="3">
+      <c r="AQ10" s="3">
         <v>440600</v>
       </c>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1235,8 +1248,9 @@
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
       <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1357,8 +1371,11 @@
       <c r="AP12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AQ12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1479,252 +1496,261 @@
       <c r="AP13" s="3">
         <v>0</v>
       </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>4000</v>
+      </c>
+      <c r="E14" s="3">
         <v>67000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>7000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>10000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>22000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>42000</v>
       </c>
-      <c r="I14" s="3">
-        <v>56000</v>
-      </c>
       <c r="J14" s="3">
+        <v>-171000</v>
+      </c>
+      <c r="K14" s="3">
         <v>10000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>4000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>3000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>25000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>123000</v>
       </c>
-      <c r="O14" s="3" t="s">
+      <c r="P14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>-779000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>-97600</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>-1600</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>-5400</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>-1600</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>100</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>-500</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>-700</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>-300</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>2300</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>-2200</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>-4500</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>625800</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>-300</v>
       </c>
-      <c r="AD14" s="3">
-        <v>0</v>
-      </c>
       <c r="AE14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF14" s="3">
         <v>3000</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>-100</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>-300</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>-200</v>
-      </c>
-      <c r="AI14" s="3">
-        <v>-100</v>
       </c>
       <c r="AJ14" s="3">
         <v>-100</v>
       </c>
       <c r="AK14" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AL14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM14" s="3">
         <v>20000</v>
       </c>
-      <c r="AM14" s="3">
+      <c r="AN14" s="3">
         <v>-600</v>
       </c>
-      <c r="AN14" s="3">
-        <v>0</v>
-      </c>
       <c r="AO14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP14" s="3">
         <v>-100</v>
       </c>
-      <c r="AP14" s="3">
+      <c r="AQ14" s="3">
         <v>-5700</v>
       </c>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>387000</v>
+      </c>
+      <c r="E15" s="3">
         <v>378000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>388000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>378000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>368000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>380000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>344000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>274000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>262000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>254000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>260000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>177000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>170000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>162000</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>157400</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>157100</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>157800</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>153900</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>153100</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>154500</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>156900</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>157100</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>152600</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>153200</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>140400</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>132400</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>126000</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>121400</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>115000</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>114200</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>110600</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>107400</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>106300</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>104200</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AL15" s="3">
         <v>103800</v>
       </c>
-      <c r="AL15" s="3">
+      <c r="AM15" s="3">
         <v>102300</v>
       </c>
-      <c r="AM15" s="3">
+      <c r="AN15" s="3">
         <v>100800</v>
       </c>
-      <c r="AN15" s="3">
+      <c r="AO15" s="3">
         <v>99400</v>
       </c>
-      <c r="AO15" s="3">
+      <c r="AP15" s="3">
         <v>99300</v>
       </c>
-      <c r="AP15" s="3">
+      <c r="AQ15" s="3">
         <v>98600</v>
       </c>
     </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1764,252 +1790,259 @@
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
       <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
-    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>10452000</v>
+      </c>
+      <c r="E17" s="3">
         <v>8183000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>7526000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>7066000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>6434000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>6781000</v>
       </c>
-      <c r="I17" s="3">
-        <v>5376000</v>
-      </c>
       <c r="J17" s="3">
+        <v>5603000</v>
+      </c>
+      <c r="K17" s="3">
         <v>3885000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>3661000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>3714000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>4111000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>3327000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>2995000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>3803000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>4275200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>5214300</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>5307800</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>4782200</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>4768300</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>3868300</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>2777500</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>2530000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>2031800</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>1621600</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>1300800</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>2242100</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>2176300</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>1781100</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>1981400</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>2311200</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>2664800</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>2898400</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>2512200</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>2682400</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>3391600</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>2556000</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>2406300</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>2432500</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>2324900</v>
       </c>
-      <c r="AP17" s="3">
+      <c r="AQ17" s="3">
         <v>2028600</v>
       </c>
     </row>
-    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>1597000</v>
+      </c>
+      <c r="E18" s="3">
         <v>1435000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>1539000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>1568000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>1453000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>1262000</v>
       </c>
-      <c r="I18" s="3">
-        <v>1624000</v>
-      </c>
       <c r="J18" s="3">
+        <v>1397000</v>
+      </c>
+      <c r="K18" s="3">
         <v>1138000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>1233000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>1067000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>1124000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>862000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>737000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>718000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>756800</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>699200</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>688900</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>662400</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>652200</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>667900</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>611500</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>664700</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>538800</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>552700</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>359900</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-105400</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>487300</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>482100</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>476200</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>468800</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>471900</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>495500</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>448300</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>419700</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>400600</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>350400</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>319500</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>317100</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>329600</v>
       </c>
-      <c r="AP18" s="3">
+      <c r="AQ18" s="3">
         <v>329400</v>
       </c>
     </row>
-    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -2052,618 +2085,634 @@
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
       <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
-    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-107000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-92000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-173000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-129000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-120000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-110000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-208000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-109000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-92000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-83000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-116000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-71000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-56000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-48000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>36500</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>31600</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>26900</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>23200</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>36000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>30100</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>25600</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>29100</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>41400</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>42600</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>36500</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>48700</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>60400</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>54000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>52200</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>61800</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>36100</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>43300</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>34900</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>37800</v>
-      </c>
-      <c r="AK20" s="3">
-        <v>39800</v>
       </c>
       <c r="AL20" s="3">
         <v>39800</v>
       </c>
       <c r="AM20" s="3">
+        <v>39800</v>
+      </c>
+      <c r="AN20" s="3">
         <v>18800</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>40500</v>
       </c>
-      <c r="AO20" s="3">
+      <c r="AP20" s="3">
         <v>34200</v>
       </c>
-      <c r="AP20" s="3">
+      <c r="AQ20" s="3">
         <v>38700</v>
       </c>
     </row>
-    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>2091000</v>
+      </c>
+      <c r="E21" s="3">
         <v>1905000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>2100000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>2075000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>1941000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>1752000</v>
       </c>
-      <c r="I21" s="3">
-        <v>2176000</v>
-      </c>
       <c r="J21" s="3">
+        <v>1949000</v>
+      </c>
+      <c r="K21" s="3">
         <v>1521000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1587000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1404000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>1500000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>1110000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>963000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>928000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>950700</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>887900</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>873600</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>839500</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>841300</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>852500</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>794100</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>851000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>732800</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>748500</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>536800</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>75700</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>673700</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>657500</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>643400</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>644700</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>618600</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>646200</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>589500</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>561800</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>544100</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>492500</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>439200</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>457000</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>463100</v>
       </c>
-      <c r="AP21" s="3">
+      <c r="AQ21" s="3">
         <v>466600</v>
       </c>
     </row>
-    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>434000</v>
+      </c>
+      <c r="E22" s="3">
         <v>439000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>453000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>450000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>438000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>442000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>448000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>325000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>298000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>300000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>305000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>215000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>180000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>166000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>166200</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>166900</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>170800</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>172100</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>178400</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>184000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>185000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>185500</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>176900</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>176400</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>219000</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>140600</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>129300</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>129600</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>117500</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>115400</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>118500</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>121900</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>113500</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>115700</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>124200</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AM22" s="3">
         <v>126500</v>
       </c>
-      <c r="AM22" s="3">
+      <c r="AN22" s="3">
         <v>118500</v>
       </c>
-      <c r="AN22" s="3">
+      <c r="AO22" s="3">
         <v>116500</v>
       </c>
-      <c r="AO22" s="3">
+      <c r="AP22" s="3">
         <v>114200</v>
       </c>
-      <c r="AP22" s="3">
+      <c r="AQ22" s="3">
         <v>118200</v>
       </c>
     </row>
-    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>1266000</v>
+      </c>
+      <c r="E23" s="3">
         <v>1021000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>1252000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>1237000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>1113000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>888000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>1328000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>912000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>1023000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>847000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>910000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>595000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>613000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>1379000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>627100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>563900</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>545100</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>513600</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>509800</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>513900</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>452200</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>508300</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>403200</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>418900</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>177500</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-197300</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>418400</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>406500</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>410900</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>415100</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>389500</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>416900</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>369700</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>341800</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>316200</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>263700</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>219800</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>241100</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>249600</v>
       </c>
-      <c r="AP23" s="3">
+      <c r="AQ23" s="3">
         <v>249800</v>
       </c>
     </row>
-    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>299000</v>
+      </c>
+      <c r="E24" s="3">
         <v>245000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>274000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>297000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>260000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>197000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>328000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>219000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>243000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>208000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>222000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>141000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>145000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>330000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>142200</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>132100</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>130700</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>122400</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>130400</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>121900</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>110100</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>122100</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>95200</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>106600</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>43100</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>-55400</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>98200</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>97400</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>98900</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>77900</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>96600</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>103000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>87500</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>75800</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>110100</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>97100</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>43800</v>
-      </c>
-      <c r="AN24" s="3">
-        <v>54900</v>
       </c>
       <c r="AO24" s="3">
         <v>54900</v>
       </c>
       <c r="AP24" s="3">
+        <v>54900</v>
+      </c>
+      <c r="AQ24" s="3">
         <v>55000</v>
       </c>
     </row>
-    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2784,252 +2833,261 @@
       <c r="AP25" s="3">
         <v>0</v>
       </c>
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>967000</v>
+      </c>
+      <c r="E26" s="3">
         <v>776000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>978000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>940000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>853000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>691000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>1000000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>693000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>780000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>639000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>688000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>454000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>468000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>1049000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>484900</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>431800</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>414400</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>391200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>379400</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>392000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>342100</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>386200</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>308000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>312300</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>134300</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-141900</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>320300</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>309200</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>312000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>337200</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>292900</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>313900</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>282200</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>266000</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>206100</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>166500</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>176000</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>186200</v>
-      </c>
-      <c r="AO26" s="3">
-        <v>194800</v>
       </c>
       <c r="AP26" s="3">
         <v>194800</v>
       </c>
+      <c r="AQ26" s="3">
+        <v>194800</v>
+      </c>
     </row>
-    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>966000</v>
+      </c>
+      <c r="E27" s="3">
         <v>774000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>977000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>939000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>841000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>636000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>923000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>692000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>780000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>639000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>688000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>453000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>468000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>1049000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>484600</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>431500</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>414100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>390900</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>379100</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>391700</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>341900</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>385900</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>307800</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>312000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>134000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-142100</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>320000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>308900</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>311700</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>336900</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>292600</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>313000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>280800</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>264200</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>204100</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>165500</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>71500</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>87400</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>90800</v>
       </c>
-      <c r="AP27" s="3">
+      <c r="AQ27" s="3">
         <v>92700</v>
       </c>
     </row>
-    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3150,8 +3208,11 @@
       <c r="AP28" s="3">
         <v>0</v>
       </c>
+      <c r="AQ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3236,17 +3297,17 @@
       <c r="AD29" s="3">
         <v>0</v>
       </c>
-      <c r="AE29" s="3" t="s">
-        <v>8</v>
+      <c r="AE29" s="3">
+        <v>0</v>
       </c>
       <c r="AF29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AG29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AH29" s="3" t="s">
+      <c r="AG29" s="3" t="s">
         <v>8</v>
+      </c>
+      <c r="AH29" s="3">
+        <v>0</v>
       </c>
       <c r="AI29" s="3" t="s">
         <v>8</v>
@@ -3254,12 +3315,12 @@
       <c r="AJ29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AK29" s="3">
+      <c r="AK29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AL29" s="3">
         <v>-141300</v>
       </c>
-      <c r="AL29" s="3">
-        <v>0</v>
-      </c>
       <c r="AM29" s="3">
         <v>0</v>
       </c>
@@ -3267,13 +3328,16 @@
         <v>0</v>
       </c>
       <c r="AO29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP29" s="3">
         <v>-300</v>
       </c>
-      <c r="AP29" s="3">
+      <c r="AQ29" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3394,8 +3458,11 @@
       <c r="AP30" s="3">
         <v>0</v>
       </c>
+      <c r="AQ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3516,252 +3583,261 @@
       <c r="AP31" s="3">
         <v>0</v>
       </c>
+      <c r="AQ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>107000</v>
+      </c>
+      <c r="E32" s="3">
         <v>92000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>173000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>129000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>120000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>110000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>208000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>109000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>92000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>83000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>116000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>71000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>56000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>48000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-36500</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-31600</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-26900</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-23200</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-36000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-30100</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-25600</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-29100</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-41400</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-42600</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-36500</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-48700</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-60400</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-54000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-52200</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-61800</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-36100</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-43300</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-34900</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-37800</v>
-      </c>
-      <c r="AK32" s="3">
-        <v>-39800</v>
       </c>
       <c r="AL32" s="3">
         <v>-39800</v>
       </c>
       <c r="AM32" s="3">
+        <v>-39800</v>
+      </c>
+      <c r="AN32" s="3">
         <v>-18800</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>-40500</v>
       </c>
-      <c r="AO32" s="3">
+      <c r="AP32" s="3">
         <v>-34200</v>
       </c>
-      <c r="AP32" s="3">
+      <c r="AQ32" s="3">
         <v>-38700</v>
       </c>
     </row>
-    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>966000</v>
+      </c>
+      <c r="E33" s="3">
         <v>774000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>977000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>939000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>841000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>636000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>923000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>693000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>780000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>639000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>688000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>454000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>468000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>1049000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>484600</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>431500</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>414100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>390900</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>379100</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>391700</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>341900</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>385900</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>307800</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>312000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>134000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-142100</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>320000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>308900</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>311700</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>336900</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>292600</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>313000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>280800</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>264200</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>62800</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>165500</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>71500</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>87400</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>90500</v>
       </c>
-      <c r="AP33" s="3">
+      <c r="AQ33" s="3">
         <v>92100</v>
       </c>
     </row>
-    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3882,257 +3958,266 @@
       <c r="AP34" s="3">
         <v>0</v>
       </c>
+      <c r="AQ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>966000</v>
+      </c>
+      <c r="E35" s="3">
         <v>774000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>977000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>939000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>841000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>636000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>923000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>693000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>780000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>639000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>688000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>454000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>468000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>1049000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>484600</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>431500</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>414100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>390900</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>379100</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>391700</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>341900</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>385900</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>307800</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>312000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>134000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-142100</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>320000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>308900</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>311700</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>336900</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>292600</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>313000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>280800</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>264200</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>62800</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>165500</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>71500</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>87400</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>90500</v>
       </c>
-      <c r="AP35" s="3">
+      <c r="AQ35" s="3">
         <v>92100</v>
       </c>
     </row>
-    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43830</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43738</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43646</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43555</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43465</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43373</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43190</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43100</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>43008</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42916</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42825</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42735</v>
       </c>
-      <c r="AP38" s="2">
+      <c r="AQ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4175,8 +4260,9 @@
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
       <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
     </row>
-    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4219,130 +4305,134 @@
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
       <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
     </row>
-    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>161000</v>
+      </c>
+      <c r="E41" s="3">
         <v>172000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>78000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1199000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>97000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>141000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>733000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>579000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>36000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>65000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>338000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>284000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>106000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>680000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>220200</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>22200</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>135800</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>14600</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>146400</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>224300</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>374400</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>402400</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>524500</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>447100</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>945700</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>531600</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>21000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>673300</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>273400</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>27800</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>12000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>84500</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>15300</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>17500</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>37200</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>11700</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>332400</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>310800</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>248900</v>
       </c>
-      <c r="AP41" s="3">
+      <c r="AQ41" s="3">
         <v>237400</v>
       </c>
     </row>
-    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4380,14 +4470,14 @@
         <v>0</v>
       </c>
       <c r="O42" s="3">
+        <v>0</v>
+      </c>
+      <c r="P42" s="3">
         <v>17000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>1000</v>
       </c>
-      <c r="Q42" s="3">
-        <v>0</v>
-      </c>
       <c r="R42" s="3">
         <v>0</v>
       </c>
@@ -4463,862 +4553,886 @@
       <c r="AP42" s="3">
         <v>0</v>
       </c>
+      <c r="AQ42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>3550000</v>
+      </c>
+      <c r="E43" s="3">
         <v>3670000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>3010000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>2580000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>2484000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>2651000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>2326000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1252000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1330000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1699000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1705000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1571000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1023000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>1153000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>1532300</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>1729200</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>1778700</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>1682500</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>1441800</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>1497500</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>1092000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>910000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>829800</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>717900</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>608900</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>497600</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>836400</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>721100</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>670600</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>814200</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>820700</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>1088000</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>934700</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>844200</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>1203000</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>939600</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>749300</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>734800</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AP43" s="3">
         <v>872400</v>
       </c>
-      <c r="AP43" s="3">
+      <c r="AQ43" s="3">
         <v>737200</v>
       </c>
     </row>
-    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1056000</v>
+      </c>
+      <c r="E44" s="3">
         <v>1136000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>948000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>871000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>858000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>905000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>748000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>773000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>824000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>951000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>639000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>1011000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>460000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>556000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>623700</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>732700</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>823200</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>757000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>620500</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>798300</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>614500</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>530000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>382900</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>472800</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>532900</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>400000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>531900</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>495800</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>388900</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>445300</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>466900</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>577000</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>426400</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>323000</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>432600</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>391600</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AN44" s="3">
         <v>275300</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AO44" s="3">
         <v>193300</v>
       </c>
-      <c r="AO44" s="3">
+      <c r="AP44" s="3">
         <v>200900</v>
       </c>
-      <c r="AP44" s="3">
+      <c r="AQ44" s="3">
         <v>299500</v>
       </c>
     </row>
-    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>543000</v>
+      </c>
+      <c r="E45" s="3">
         <v>353000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>452000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>535000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>457000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>374000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>431000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>272000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>285000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>235000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>426000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>322000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>257000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>179000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>171500</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>281200</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>288900</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>187200</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>165700</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>146700</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>154800</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>155200</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>132500</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>83600</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>92300</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>59100</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>81000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>77400</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>68300</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>55500</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>99100</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>58400</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>57300</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>106100</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>91700</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>176000</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>90800</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>139500</v>
       </c>
-      <c r="AO45" s="3">
+      <c r="AP45" s="3">
         <v>107400</v>
       </c>
-      <c r="AP45" s="3">
+      <c r="AQ45" s="3">
         <v>95200</v>
       </c>
     </row>
-    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>5310000</v>
+      </c>
+      <c r="E46" s="3">
         <v>5543000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>4488000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>5185000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>3896000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>4116000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>4238000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>2876000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>2475000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>2950000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>3108000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>3188000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1863000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>2569000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>2547800</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>2765300</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>3026500</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>2641300</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>2374400</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>2666900</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>2235600</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>1997600</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>1869800</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>1721400</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>2179900</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>1488300</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>1470300</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>1967600</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>1401200</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>1342800</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>1398600</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>1807900</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>1433700</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>1290700</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>1764500</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>1518900</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>1447800</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>1378400</v>
       </c>
-      <c r="AO46" s="3">
+      <c r="AP46" s="3">
         <v>1429700</v>
       </c>
-      <c r="AP46" s="3">
+      <c r="AQ46" s="3">
         <v>1369300</v>
       </c>
     </row>
-    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>3139000</v>
+      </c>
+      <c r="E47" s="3">
         <v>2985000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>2889000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>2773000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>2446000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>2405000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>2316000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>1925000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>1937000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>1939000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>1874000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>1795000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>885000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>789000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>801800</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>803800</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>801300</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>797400</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>797600</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>797200</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>800400</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>807700</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>805000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>790400</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>790000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>810500</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>865500</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>874200</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>885100</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>955100</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>973700</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>986400</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>987000</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>997400</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>1003200</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>1013700</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AN47" s="3">
         <v>944600</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AO47" s="3">
         <v>956400</v>
       </c>
-      <c r="AO47" s="3">
+      <c r="AP47" s="3">
         <v>958800</v>
       </c>
-      <c r="AP47" s="3">
+      <c r="AQ47" s="3">
         <v>943400</v>
       </c>
     </row>
-    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>48774000</v>
+      </c>
+      <c r="E48" s="3">
         <v>48304000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>48106000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>47158000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>46715000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>46230000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>46155000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>33613000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>33415000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>32807000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>32801000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>32089000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>20229000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>20040000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>19952500</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>19789800</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>19601200</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>19425200</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>19319900</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>19221900</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>19181500</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>19125300</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>19154900</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>19029300</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>18981200</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>18629500</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>18363800</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>17379000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>16353600</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>15518000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>14766700</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>13960500</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>13303900</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>12878200</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>12698100</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>12578600</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>12547000</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>12553600</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>12571400</v>
       </c>
-      <c r="AP48" s="3">
+      <c r="AQ48" s="3">
         <v>12526700</v>
       </c>
     </row>
-    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>10893000</v>
+      </c>
+      <c r="E49" s="3">
         <v>10926000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>10959000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>11043000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>11066000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>11096000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>11130000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>6431000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>6409000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>6367000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>6268000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>6543000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>748000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>750000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>752900</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>755500</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>758100</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>760700</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>763300</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>765900</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>768500</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>771100</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>773700</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>776300</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>778900</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>781500</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>957800</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>960800</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>963800</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>964200</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>967100</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>970100</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>987500</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>990500</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>993500</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>996400</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>999400</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>1002400</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AP49" s="3">
         <v>1005400</v>
       </c>
-      <c r="AP49" s="3">
+      <c r="AQ49" s="3">
         <v>1008300</v>
       </c>
     </row>
-    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5439,8 +5553,11 @@
       <c r="AP50" s="3">
         <v>0</v>
       </c>
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5561,130 +5678,136 @@
       <c r="AP51" s="3">
         <v>0</v>
       </c>
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>433000</v>
+      </c>
+      <c r="E52" s="3">
         <v>445000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>199000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>457000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>401000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>416000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>230000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>6205000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>299000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>327000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>215000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>324000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>313000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>316000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>324100</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>324800</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>339700</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>368100</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>366500</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>420400</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>451200</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>478200</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>475300</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>463500</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>262500</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>259600</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>154600</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>154300</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>147900</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>154200</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>125600</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>186400</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>201600</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>275500</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>386700</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>657200</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>734100</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>176800</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AP52" s="3">
         <v>173500</v>
       </c>
-      <c r="AP52" s="3">
+      <c r="AQ52" s="3">
         <v>134300</v>
       </c>
     </row>
-    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5805,130 +5928,136 @@
       <c r="AP53" s="3">
         <v>0</v>
       </c>
+      <c r="AQ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>68549000</v>
+      </c>
+      <c r="E54" s="3">
         <v>68203000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>66641000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>66616000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>64524000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>64263000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>64069000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>51050000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>44535000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>44390000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>44266000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>43939000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>24038000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>24464000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>24379100</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>24439200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>24526800</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>23992700</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>23621600</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>23872300</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>23437200</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>23179900</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>23078800</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>22780900</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>22992500</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>21969400</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>21812100</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>21335900</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>19751600</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>18934300</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>18231700</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>17911300</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>16913700</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>16432300</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>16845900</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>16764800</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>16672900</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>16067600</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>16138800</v>
       </c>
-      <c r="AP54" s="3">
+      <c r="AQ54" s="3">
         <v>15982000</v>
       </c>
     </row>
-    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5971,8 +6100,9 @@
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
       <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -6015,198 +6145,202 @@
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
       <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>3533000</v>
+      </c>
+      <c r="E57" s="3">
         <v>3572000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2838000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2569000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2453000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>2437000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>2187000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1247000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1271000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1480000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1564000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1619000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>880000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1074000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1359500</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1658900</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1923800</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>1729900</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>1332400</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>1443000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>1052600</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>929800</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>719300</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>624500</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>755500</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>742400</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>1209900</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>1129800</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>907400</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>1027300</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>1116300</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>1339500</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>1027500</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>773100</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>1140600</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>922800</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>696800</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>703300</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AP57" s="3">
         <v>874700</v>
       </c>
-      <c r="AP57" s="3">
+      <c r="AQ57" s="3">
         <v>711800</v>
       </c>
     </row>
-    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>2249000</v>
+      </c>
+      <c r="E58" s="3">
         <v>2888000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>2115000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>1741000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>2842000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>2259000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>1121000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>1257000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1534000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1554000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>507000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>532000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>16000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>512000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>925000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>1826300</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>895800</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>973800</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>895800</v>
-      </c>
-      <c r="V58" s="3">
-        <v>536100</v>
       </c>
       <c r="W58" s="3">
         <v>536100</v>
       </c>
       <c r="X58" s="3">
+        <v>536100</v>
+      </c>
+      <c r="Y58" s="3">
         <v>543800</v>
-      </c>
-      <c r="Y58" s="3">
-        <v>7700</v>
       </c>
       <c r="Z58" s="3">
         <v>7700</v>
@@ -6218,537 +6352,552 @@
         <v>7700</v>
       </c>
       <c r="AC58" s="3">
+        <v>7700</v>
+      </c>
+      <c r="AD58" s="3">
         <v>229600</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>9600</v>
-      </c>
-      <c r="AE58" s="3">
-        <v>309500</v>
       </c>
       <c r="AF58" s="3">
         <v>309500</v>
       </c>
       <c r="AG58" s="3">
+        <v>309500</v>
+      </c>
+      <c r="AH58" s="3">
         <v>509400</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>627700</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>1088700</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>932700</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>1047300</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>1364900</v>
       </c>
-      <c r="AM58" s="3">
+      <c r="AN58" s="3">
         <v>1769100</v>
       </c>
-      <c r="AN58" s="3">
+      <c r="AO58" s="3">
         <v>1701400</v>
       </c>
-      <c r="AO58" s="3">
+      <c r="AP58" s="3">
         <v>1520900</v>
       </c>
-      <c r="AP58" s="3">
+      <c r="AQ58" s="3">
         <v>1154200</v>
       </c>
     </row>
-    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>963000</v>
+      </c>
+      <c r="E59" s="3">
         <v>836000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>913000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>975000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>877000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>1026000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>900000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>800000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>819000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>892000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1000000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>929000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>407000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>459000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>767200</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>653500</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>835300</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>778800</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>956400</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>823800</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>805900</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>574400</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>617600</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>462000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>510000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>341400</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>580800</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>427800</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>520500</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>352900</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>482700</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>483000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>456000</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>345100</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>479400</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>453400</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>394600</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>327300</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>441000</v>
       </c>
-      <c r="AP59" s="3">
+      <c r="AQ59" s="3">
         <v>476000</v>
       </c>
     </row>
-    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>7204000</v>
+      </c>
+      <c r="E60" s="3">
         <v>7811000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>6365000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>5735000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>6646000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>6183000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>4719000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>3557000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>3979000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>4194000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>3452000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>3298000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>1517000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>2182000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>3051600</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>4138600</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>3654800</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>3482600</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>3184600</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>2802900</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>2394600</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>2048000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>1344500</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>1094100</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>1273100</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>1091400</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>2020300</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>1567200</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>1737400</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>1689700</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>2108400</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>2450200</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>2572100</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>2050800</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>2667300</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>2741100</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>2860500</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>2732000</v>
       </c>
-      <c r="AO60" s="3">
+      <c r="AP60" s="3">
         <v>2836700</v>
       </c>
-      <c r="AP60" s="3">
+      <c r="AQ60" s="3">
         <v>2342000</v>
       </c>
     </row>
-    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>30773000</v>
+      </c>
+      <c r="E61" s="3">
         <v>30764000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>30938000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>31986000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>29625000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>29781000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>31172000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>26880000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>20339000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>20447000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>21257000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>21527000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>12805000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>12794000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>12695800</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>11950700</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>12872700</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>12750500</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>12747600</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>13640500</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>13637600</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>13638800</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>14228400</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>14249300</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>14276200</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>14146700</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>12504100</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>12504300</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>10779400</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>10030100</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>8899600</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>8325700</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>7091200</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>7091800</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>8091600</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>8092000</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>7835600</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>7919800</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>7920000</v>
       </c>
-      <c r="AP61" s="3">
+      <c r="AQ61" s="3">
         <v>8320100</v>
       </c>
     </row>
-    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>599000</v>
+      </c>
+      <c r="E62" s="3">
         <v>609000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>420000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>626000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>574000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>588000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>594000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>534000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>512000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>559000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>479000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>423000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>330000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>329000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>2137700</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>2037700</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>1884700</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>1765900</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>1674200</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>1588100</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>1494700</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>1396200</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>1463400</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>1291300</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>1202500</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>1170800</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>1061800</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>1045600</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>886700</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>772500</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>644100</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>482600</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>411900</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>420500</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>401600</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>415400</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>411600</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>1946200</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AP62" s="3">
         <v>1953100</v>
       </c>
-      <c r="AP62" s="3">
+      <c r="AQ62" s="3">
         <v>1879700</v>
       </c>
     </row>
-    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6869,8 +7018,11 @@
       <c r="AP63" s="3">
         <v>0</v>
       </c>
+      <c r="AQ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6991,8 +7143,11 @@
       <c r="AP64" s="3">
         <v>0</v>
       </c>
+      <c r="AQ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -7113,130 +7268,136 @@
       <c r="AP65" s="3">
         <v>0</v>
       </c>
+      <c r="AQ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>45468000</v>
+      </c>
+      <c r="E66" s="3">
         <v>45715000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>44072000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>44459000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>42620000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>42143000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>41936000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>34163000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>27826000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>27945000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>27782000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>27640000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>16820000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>17332000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>17885200</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>18127000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>18412200</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>17999000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>17606500</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>18031500</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>17526900</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>17083000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>17036400</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>16634800</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>16751800</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>16408800</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>15586200</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>15117000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>13403500</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>12492300</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>11652100</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>11258600</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>10248900</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>9730900</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>11318100</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>11405300</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>11265200</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>15829200</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>15950000</v>
       </c>
-      <c r="AP66" s="3">
+      <c r="AQ66" s="3">
         <v>15767700</v>
       </c>
     </row>
-    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7279,8 +7440,9 @@
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
       <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7401,8 +7563,11 @@
       <c r="AP68" s="3">
         <v>0</v>
       </c>
+      <c r="AQ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7523,8 +7688,11 @@
       <c r="AP69" s="3">
         <v>0</v>
       </c>
+      <c r="AQ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7645,8 +7813,11 @@
       <c r="AP70" s="3">
         <v>0</v>
       </c>
+      <c r="AQ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7767,56 +7938,59 @@
       <c r="AP71" s="3">
         <v>0</v>
       </c>
+      <c r="AQ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>2759000</v>
+      </c>
+      <c r="E72" s="3">
         <v>2469000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>2373000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>2048000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>1765000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>1569000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>1579000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>1237000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>1126000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>927000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>868000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>737000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>711000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>672000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>50400</v>
       </c>
-      <c r="R72" s="3">
-        <v>0</v>
-      </c>
       <c r="S72" s="3">
         <v>0</v>
       </c>
@@ -7829,12 +8003,12 @@
       <c r="V72" s="3">
         <v>0</v>
       </c>
-      <c r="W72" s="3" t="s">
+      <c r="W72" s="3">
+        <v>0</v>
+      </c>
+      <c r="X72" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="X72" s="3">
-        <v>0</v>
-      </c>
       <c r="Y72" s="3">
         <v>0</v>
       </c>
@@ -7842,26 +8016,26 @@
         <v>0</v>
       </c>
       <c r="AA72" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB72" s="3">
         <v>-7500</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-141900</v>
       </c>
-      <c r="AC72" s="3">
-        <v>0</v>
-      </c>
       <c r="AD72" s="3">
         <v>0</v>
       </c>
       <c r="AE72" s="3">
         <v>0</v>
       </c>
-      <c r="AF72" s="3" t="s">
+      <c r="AF72" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG72" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AG72" s="3">
-        <v>0</v>
-      </c>
       <c r="AH72" s="3">
         <v>0</v>
       </c>
@@ -7881,16 +8055,19 @@
         <v>0</v>
       </c>
       <c r="AN72" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO72" s="3">
         <v>30900</v>
       </c>
-      <c r="AO72" s="3">
-        <v>0</v>
-      </c>
       <c r="AP72" s="3">
         <v>0</v>
       </c>
+      <c r="AQ72" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -8011,8 +8188,11 @@
       <c r="AP73" s="3">
         <v>0</v>
       </c>
+      <c r="AQ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -8133,8 +8313,11 @@
       <c r="AP74" s="3">
         <v>0</v>
       </c>
+      <c r="AQ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8255,130 +8438,136 @@
       <c r="AP75" s="3">
         <v>0</v>
       </c>
+      <c r="AQ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>22937000</v>
+      </c>
+      <c r="E76" s="3">
         <v>22357000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>22485000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>22081000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>21830000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>21364000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>17036000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>16887000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>16709000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>16445000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>16484000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>16299000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>7218000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>7132000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>6493900</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>6312300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>6114600</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>5993700</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>6015200</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>5840900</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>5910400</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>6097000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>6042400</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>6146100</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>6240700</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>5560600</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>6226000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>6218900</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>6348100</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>6442000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>6579500</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>6652800</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>6664900</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>6701400</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>5527900</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>5359500</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>5407700</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>238400</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>188700</v>
       </c>
-      <c r="AP76" s="3">
+      <c r="AQ76" s="3">
         <v>214300</v>
       </c>
     </row>
-    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8499,257 +8688,266 @@
       <c r="AP77" s="3">
         <v>0</v>
       </c>
+      <c r="AQ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43830</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43738</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43646</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43555</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43465</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43373</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43190</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43100</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>43008</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42916</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42825</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42735</v>
       </c>
-      <c r="AP80" s="2">
+      <c r="AQ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>966000</v>
+      </c>
+      <c r="E81" s="3">
         <v>774000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>977000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>939000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>841000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>636000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>923000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>693000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>780000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>639000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>688000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>454000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>468000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>1049000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>484600</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>431500</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>414100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>390900</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>379100</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>391700</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>341900</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>385900</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>307800</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>312000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>134000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-142100</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>320000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>308900</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>311700</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>336900</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>292600</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>313000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>280800</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>264200</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>62800</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>165500</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>71500</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>87400</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>90500</v>
       </c>
-      <c r="AP81" s="3">
+      <c r="AQ81" s="3">
         <v>92100</v>
       </c>
     </row>
-    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8792,130 +8990,134 @@
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
       <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>368000</v>
+      </c>
+      <c r="E83" s="3">
         <v>380000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>282000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>274000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>262000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>254000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>227000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>177000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>170000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>162000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>147000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>157000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>158000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>154000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>157400</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>157100</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>157800</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>153900</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>153100</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>154500</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>156900</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>157100</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>152600</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>153200</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>140400</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>132400</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>126000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>121400</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>115000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>114200</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>110600</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>107400</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>106300</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>104200</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>103800</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>102300</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>100800</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>99400</v>
       </c>
-      <c r="AO83" s="3">
+      <c r="AP83" s="3">
         <v>99300</v>
       </c>
-      <c r="AP83" s="3">
+      <c r="AQ83" s="3">
         <v>98600</v>
       </c>
     </row>
-    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -9036,8 +9238,11 @@
       <c r="AP84" s="3">
         <v>0</v>
       </c>
+      <c r="AQ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -9158,8 +9363,11 @@
       <c r="AP85" s="3">
         <v>0</v>
       </c>
+      <c r="AQ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9280,8 +9488,11 @@
       <c r="AP86" s="3">
         <v>0</v>
       </c>
+      <c r="AQ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9402,8 +9613,11 @@
       <c r="AP87" s="3">
         <v>0</v>
       </c>
+      <c r="AQ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9524,130 +9738,136 @@
       <c r="AP88" s="3">
         <v>0</v>
       </c>
+      <c r="AQ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>2053000</v>
+      </c>
+      <c r="E89" s="3">
         <v>934000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>1546000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>1624000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>1525000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>904000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>1611000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>1251000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1430000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>596000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>1508000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>920000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>772000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>1221000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>1040400</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>615900</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>787400</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>462200</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>1055100</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>413200</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>544700</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>533300</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>795900</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>366700</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>313700</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>422700</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>619900</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>358900</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>614300</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>353600</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>670300</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>513500</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>507600</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>495300</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>379400</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>293100</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>373800</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>269100</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>431400</v>
       </c>
-      <c r="AP89" s="3">
+      <c r="AQ89" s="3">
         <v>390500</v>
       </c>
     </row>
-    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9690,130 +9910,134 @@
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
       <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-613000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-864000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-970000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-804000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-749000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-629000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-562000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-468000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-479000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-512000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-603000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-398000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-305000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-289000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-316000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-326700</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-302300</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-257000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-206500</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-166200</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-147400</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-176700</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-271400</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-380000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-594300</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-949700</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-1109000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-1019200</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-830500</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-889700</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-831800</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-694300</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-350900</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-264500</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-182000</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-135200</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-82500</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-112700</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>-757700</v>
       </c>
-      <c r="AP91" s="3">
+      <c r="AQ91" s="3">
         <v>-158300</v>
       </c>
     </row>
-    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9934,8 +10158,11 @@
       <c r="AP92" s="3">
         <v>0</v>
       </c>
+      <c r="AQ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -10056,130 +10283,136 @@
       <c r="AP93" s="3">
         <v>0</v>
       </c>
+      <c r="AQ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-782000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-1007000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-1109000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-1134000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-814000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-694000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-4780000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-498000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-756000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-578000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-645000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-5406000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-400000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>47000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-275400</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-321100</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-299100</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-243700</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-189900</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-150900</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-153900</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-170700</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-288700</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-427000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-590100</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-964800</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-1120900</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-1015800</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-767200</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-864800</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-825100</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-688400</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-345700</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-255700</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-173000</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-210900</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-74300</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-109500</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>-130900</v>
       </c>
-      <c r="AP94" s="3">
+      <c r="AQ94" s="3">
         <v>-186100</v>
       </c>
     </row>
-    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -10222,130 +10455,134 @@
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
       <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
     </row>
-    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
         <v>674000</v>
       </c>
-      <c r="E96" s="3" t="s">
+      <c r="E96" s="3">
+        <v>674000</v>
+      </c>
+      <c r="F96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>648000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>644000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>643000</v>
-      </c>
-      <c r="I96" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="J96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K96" s="3">
-        <v>578000</v>
+      <c r="K96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L96" s="3">
         <v>578000</v>
       </c>
-      <c r="M96" s="3" t="s">
-        <v>8</v>
+      <c r="M96" s="3">
+        <v>578000</v>
       </c>
       <c r="N96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O96" s="3">
+      <c r="O96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P96" s="3">
         <v>428000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>427000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-418200</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-418100</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-417900</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-417400</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-417200</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-417100</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-416900</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-416200</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-415800</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-415600</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-387600</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-386400</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-378000</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-367600</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-357100</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-353900</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-352000</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-339600</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-327100</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AK96" s="3">
         <v>-316400</v>
       </c>
-      <c r="AK96" s="3">
+      <c r="AL96" s="3">
         <v>-286000</v>
       </c>
-      <c r="AL96" s="3">
+      <c r="AM96" s="3">
         <v>-283700</v>
       </c>
-      <c r="AM96" s="3">
+      <c r="AN96" s="3">
         <v>-129900</v>
       </c>
-      <c r="AN96" s="3">
+      <c r="AO96" s="3">
         <v>-129800</v>
       </c>
-      <c r="AO96" s="3">
+      <c r="AP96" s="3">
         <v>-129500</v>
       </c>
-      <c r="AP96" s="3">
+      <c r="AQ96" s="3">
         <v>-129600</v>
       </c>
     </row>
-    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10466,8 +10703,11 @@
       <c r="AP97" s="3">
         <v>0</v>
       </c>
+      <c r="AQ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10588,8 +10828,11 @@
       <c r="AP98" s="3">
         <v>0</v>
       </c>
+      <c r="AQ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10710,130 +10953,136 @@
       <c r="AP99" s="3">
         <v>0</v>
       </c>
+      <c r="AQ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-1282000</v>
+      </c>
+      <c r="E100" s="3">
         <v>167000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-1558000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>612000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-755000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-802000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-2562000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>5675000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-703000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-291000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-809000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>4664000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-946000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-808000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-567100</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-408400</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-367100</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-350300</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-943200</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-412400</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-418800</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-484700</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-429900</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-438300</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>690500</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>1052700</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-151400</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>1056800</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>398500</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>527100</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-112700</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>439100</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-164100</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-259400</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-180900</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-402900</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-278000</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>-97700</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>-287400</v>
       </c>
-      <c r="AP100" s="3">
+      <c r="AQ100" s="3">
         <v>-147800</v>
       </c>
     </row>
-    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -10876,8 +11125,8 @@
       <c r="P101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q101" s="3">
-        <v>0</v>
+      <c r="Q101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R101" s="3">
         <v>0</v>
@@ -10954,126 +11203,132 @@
       <c r="AP101" s="3">
         <v>0</v>
       </c>
+      <c r="AQ101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-11000</v>
+      </c>
+      <c r="E102" s="3">
         <v>94000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-1121000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>1102000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-44000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-592000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-5731000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>6428000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-29000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-273000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>54000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>178000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-574000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>460000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>198000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-113600</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>121200</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-131800</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-77900</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-150000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-28000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-122100</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>77400</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-498600</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>414100</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>510700</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-652400</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>399900</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>245600</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>15800</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-72500</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>69200</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-2200</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-19700</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>25500</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>-320700</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>21600</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>61900</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>11500</v>
       </c>
-      <c r="AP102" s="3">
+      <c r="AQ102" s="3">
         <v>56600</v>
       </c>
     </row>
